--- a/GameDesign/Excel/Localization/Loc_Item.xlsx
+++ b/GameDesign/Excel/Localization/Loc_Item.xlsx
@@ -4124,12 +4124,12 @@
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>마력의 파편</t>
+          <t>마석</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr">
         <is>
-          <t>Mana Shard</t>
+          <t>Mana Stone</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr"/>

--- a/GameDesign/Excel/Localization/Loc_Item.xlsx
+++ b/GameDesign/Excel/Localization/Loc_Item.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -159,6 +159,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -525,8 +537,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E203"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
+  <dimension ref="A1:E211"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.210625" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
@@ -548,22 +560,22 @@
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="22" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t>키</t>
         </is>
       </c>
-      <c r="C2" s="22" t="inlineStr">
+      <c r="C2" s="25" t="inlineStr">
         <is>
           <t>한국어(원문)</t>
         </is>
       </c>
-      <c r="D2" s="22" t="inlineStr">
+      <c r="D2" s="25" t="inlineStr">
         <is>
           <t>영어</t>
         </is>
       </c>
-      <c r="E2" s="22" t="inlineStr">
+      <c r="E2" s="25" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
@@ -575,22 +587,22 @@
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E3" s="23" t="n"/>
+      <c r="E3" s="26" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -598,22 +610,22 @@
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="26" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E4" s="23" t="n"/>
+      <c r="E4" s="26" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -621,37 +633,37 @@
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n"/>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
-      <c r="E5" s="23" t="n"/>
+      <c r="E5" s="26" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -674,7 +686,7 @@
           <t>Broken Pottery Shard</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr"/>
+      <c r="E7" s="28" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -693,7 +705,7 @@
           <t>Rusty Coin</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr"/>
+      <c r="E8" s="28" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -712,7 +724,7 @@
           <t>Muddy Bead</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr"/>
+      <c r="E9" s="28" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
@@ -731,7 +743,7 @@
           <t>Bronze Mirror</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr"/>
+      <c r="E10" s="28" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -750,7 +762,7 @@
           <t>Old Artisan's Stamp</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr"/>
+      <c r="E11" s="28" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -769,7 +781,7 @@
           <t>Pioneer's Journal</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr"/>
+      <c r="E12" s="28" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,7 +800,7 @@
           <t>Wheat</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr"/>
+      <c r="E13" s="28" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -807,7 +819,7 @@
           <t>Potato</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr"/>
+      <c r="E14" s="28" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -826,7 +838,7 @@
           <t>Corn</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr"/>
+      <c r="E15" s="28" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
@@ -845,7 +857,7 @@
           <t>Ginseng</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr"/>
+      <c r="E16" s="28" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -864,7 +876,7 @@
           <t>Mutant Ginseng</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr"/>
+      <c r="E17" s="28" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -883,7 +895,7 @@
           <t>Primordial Seed</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr"/>
+      <c r="E18" s="28" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -902,7 +914,7 @@
           <t>Brushwood</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr"/>
+      <c r="E19" s="28" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -921,7 +933,7 @@
           <t>Pine Lumber</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr"/>
+      <c r="E20" s="28" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -940,7 +952,7 @@
           <t>Oak Lumber</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr"/>
+      <c r="E21" s="28" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
@@ -959,7 +971,7 @@
           <t>Ebony Lumber</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr"/>
+      <c r="E22" s="28" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -978,7 +990,7 @@
           <t>Fine Timber</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr"/>
+      <c r="E23" s="28" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -997,7 +1009,7 @@
           <t>World Tree Branch</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr"/>
+      <c r="E24" s="28" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1016,7 +1028,7 @@
           <t>Rock</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr"/>
+      <c r="E25" s="28" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1035,7 +1047,7 @@
           <t>Copper Ore</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr"/>
+      <c r="E26" s="28" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1054,7 +1066,7 @@
           <t>Silver Ore</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr"/>
+      <c r="E27" s="28" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n"/>
@@ -1073,7 +1085,7 @@
           <t>Gold Ore</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr"/>
+      <c r="E28" s="28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1092,7 +1104,7 @@
           <t>Rough Gem</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr"/>
+      <c r="E29" s="28" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1111,7 +1123,7 @@
           <t>Abyssal Gem</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr"/>
+      <c r="E30" s="28" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1130,7 +1142,7 @@
           <t>Tough Meat</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr"/>
+      <c r="E31" s="28" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1149,7 +1161,7 @@
           <t>Rabbit Hide</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr"/>
+      <c r="E32" s="28" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1168,7 +1180,7 @@
           <t>Wolf Hide</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr"/>
+      <c r="E33" s="28" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n"/>
@@ -1187,7 +1199,7 @@
           <t>Bear Fur</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr"/>
+      <c r="E34" s="28" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n"/>
@@ -1206,7 +1218,7 @@
           <t>Giant Horn</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr"/>
+      <c r="E35" s="28" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
@@ -1225,7 +1237,7 @@
           <t>Beast Heart</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr"/>
+      <c r="E36" s="28" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n"/>
@@ -1244,7 +1256,7 @@
           <t>Broken Arrowhead</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr"/>
+      <c r="E37" s="28" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n"/>
@@ -1263,7 +1275,7 @@
           <t>Rusty Helmet</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr"/>
+      <c r="E38" s="28" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n"/>
@@ -1282,7 +1294,7 @@
           <t>Rampart Crest Stone</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr"/>
+      <c r="E39" s="28" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n"/>
@@ -1301,7 +1313,7 @@
           <t>Knight's Shield</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr"/>
+      <c r="E40" s="28" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n"/>
@@ -1320,7 +1332,7 @@
           <t>Lord's Seal</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr"/>
+      <c r="E41" s="28" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n"/>
@@ -1339,7 +1351,7 @@
           <t>Guardian Knight's Sword</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr"/>
+      <c r="E42" s="28" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n"/>
@@ -1358,7 +1370,7 @@
           <t>Cracked Stone Tablet</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr"/>
+      <c r="E43" s="28" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n"/>
@@ -1377,7 +1389,7 @@
           <t>Censer Fragment</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr"/>
+      <c r="E44" s="28" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n"/>
@@ -1396,7 +1408,7 @@
           <t>Temple Candlestick</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr"/>
+      <c r="E45" s="28" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n"/>
@@ -1415,7 +1427,7 @@
           <t>Priest's Scepter</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr"/>
+      <c r="E46" s="28" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n"/>
@@ -1434,7 +1446,7 @@
           <t>Oracle Tablet</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr"/>
+      <c r="E47" s="28" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n"/>
@@ -1453,7 +1465,7 @@
           <t>Idol of a Forgotten God</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr"/>
+      <c r="E48" s="28" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n"/>
@@ -1472,7 +1484,7 @@
           <t>Old Bone Fragment</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr"/>
+      <c r="E49" s="28" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n"/>
@@ -1491,7 +1503,7 @@
           <t>Jewelry Fragment</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr"/>
+      <c r="E50" s="28" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n"/>
@@ -1510,7 +1522,7 @@
           <t>Crypt Oil Lamp</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr"/>
+      <c r="E51" s="28" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n"/>
@@ -1529,7 +1541,7 @@
           <t>Golden Mask</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr"/>
+      <c r="E52" s="28" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n"/>
@@ -1548,7 +1560,7 @@
           <t>Queen's Crown</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr"/>
+      <c r="E53" s="28" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n"/>
@@ -1567,7 +1579,7 @@
           <t>Undying Grail</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr"/>
+      <c r="E54" s="28" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n"/>
@@ -1586,7 +1598,7 @@
           <t>Ancient Coin</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr"/>
+      <c r="E55" s="28" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n"/>
@@ -1605,7 +1617,7 @@
           <t>Royal Seal Fragment</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr"/>
+      <c r="E56" s="28" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n"/>
@@ -1624,7 +1636,7 @@
           <t>Royal Document</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr"/>
+      <c r="E57" s="28" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n"/>
@@ -1643,7 +1655,7 @@
           <t>Ancient King's Scepter</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr"/>
+      <c r="E58" s="28" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n"/>
@@ -1662,7 +1674,7 @@
           <t>Royal City Map Stone</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr"/>
+      <c r="E59" s="28" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n"/>
@@ -1681,7 +1693,7 @@
           <t>Primordial Relic</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr"/>
+      <c r="E60" s="28" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n"/>
@@ -1700,7 +1712,7 @@
           <t>Barley</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr"/>
+      <c r="E61" s="28" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n"/>
@@ -1719,7 +1731,7 @@
           <t>Sweet Potato</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr"/>
+      <c r="E62" s="28" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n"/>
@@ -1738,7 +1750,7 @@
           <t>Pumpkin</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr"/>
+      <c r="E63" s="28" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n"/>
@@ -1757,7 +1769,7 @@
           <t>Prickly Pear</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr"/>
+      <c r="E64" s="28" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n"/>
@@ -1776,7 +1788,7 @@
           <t>Golden Pumpkin</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr"/>
+      <c r="E65" s="28" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n"/>
@@ -1795,7 +1807,7 @@
           <t>Undying Root</t>
         </is>
       </c>
-      <c r="E66" s="6" t="inlineStr"/>
+      <c r="E66" s="28" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n"/>
@@ -1814,7 +1826,7 @@
           <t>Rice</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr"/>
+      <c r="E67" s="28" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n"/>
@@ -1833,7 +1845,7 @@
           <t>Bean</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr"/>
+      <c r="E68" s="28" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n"/>
@@ -1852,7 +1864,7 @@
           <t>Strawberry</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr"/>
+      <c r="E69" s="28" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n"/>
@@ -1871,7 +1883,7 @@
           <t>Wild Ginseng</t>
         </is>
       </c>
-      <c r="E70" s="6" t="inlineStr"/>
+      <c r="E70" s="28" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n"/>
@@ -1890,7 +1902,7 @@
           <t>Millennium Ginseng</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr"/>
+      <c r="E71" s="28" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n"/>
@@ -1909,7 +1921,7 @@
           <t>Fruit of Life</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr"/>
+      <c r="E72" s="28" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n"/>
@@ -1928,7 +1940,7 @@
           <t>Cotton</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr"/>
+      <c r="E73" s="28" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n"/>
@@ -1947,7 +1959,7 @@
           <t>Sugarcane</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr"/>
+      <c r="E74" s="28" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n"/>
@@ -1966,7 +1978,7 @@
           <t>Coffee Cherry</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr"/>
+      <c r="E75" s="28" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n"/>
@@ -1985,7 +1997,7 @@
           <t>Black Pearl Grape</t>
         </is>
       </c>
-      <c r="E76" s="6" t="inlineStr"/>
+      <c r="E76" s="28" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n"/>
@@ -2004,7 +2016,7 @@
           <t>Rainbow Wheat</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr"/>
+      <c r="E77" s="28" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n"/>
@@ -2023,7 +2035,7 @@
           <t>World Tree Seed</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr"/>
+      <c r="E78" s="28" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n"/>
@@ -2042,7 +2054,7 @@
           <t>Purified Soil</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr"/>
+      <c r="E79" s="28" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n"/>
@@ -2061,7 +2073,7 @@
           <t>Holy Grain</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr"/>
+      <c r="E80" s="28" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n"/>
@@ -2080,7 +2092,7 @@
           <t>Elixir Herb</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr"/>
+      <c r="E81" s="28" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n"/>
@@ -2099,7 +2111,7 @@
           <t>New Moon Herb</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr"/>
+      <c r="E82" s="28" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n"/>
@@ -2118,7 +2130,7 @@
           <t>Grain of the Gods</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr"/>
+      <c r="E83" s="28" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n"/>
@@ -2137,7 +2149,7 @@
           <t>Fruit of Creation</t>
         </is>
       </c>
-      <c r="E84" s="6" t="inlineStr"/>
+      <c r="E84" s="28" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n"/>
@@ -2156,7 +2168,7 @@
           <t>Twigs</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr"/>
+      <c r="E85" s="28" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n"/>
@@ -2175,7 +2187,7 @@
           <t>Cedar Lumber</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr"/>
+      <c r="E86" s="28" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n"/>
@@ -2194,7 +2206,7 @@
           <t>Cypress Lumber</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr"/>
+      <c r="E87" s="28" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n"/>
@@ -2213,7 +2225,7 @@
           <t>Red Pine Log</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr"/>
+      <c r="E88" s="28" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n"/>
@@ -2232,7 +2244,7 @@
           <t>Millennium Pine</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr"/>
+      <c r="E89" s="28" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n"/>
@@ -2251,7 +2263,7 @@
           <t>Forest Spirit Wood</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr"/>
+      <c r="E90" s="28" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n"/>
@@ -2270,7 +2282,7 @@
           <t>Acorn Branch</t>
         </is>
       </c>
-      <c r="E91" s="6" t="inlineStr"/>
+      <c r="E91" s="28" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n"/>
@@ -2289,7 +2301,7 @@
           <t>Beech Lumber</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr"/>
+      <c r="E92" s="28" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n"/>
@@ -2308,7 +2320,7 @@
           <t>Maple Lumber</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr"/>
+      <c r="E93" s="28" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n"/>
@@ -2327,7 +2339,7 @@
           <t>Old Tree Heartwood</t>
         </is>
       </c>
-      <c r="E94" s="6" t="inlineStr"/>
+      <c r="E94" s="28" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n"/>
@@ -2346,7 +2358,7 @@
           <t>Century Oak</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr"/>
+      <c r="E95" s="28" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n"/>
@@ -2365,7 +2377,7 @@
           <t>Root of the Earth</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr"/>
+      <c r="E96" s="28" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n"/>
@@ -2384,7 +2396,7 @@
           <t>Charred Log</t>
         </is>
       </c>
-      <c r="E97" s="6" t="inlineStr"/>
+      <c r="E97" s="28" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n"/>
@@ -2403,7 +2415,7 @@
           <t>Black Oak Lumber</t>
         </is>
       </c>
-      <c r="E98" s="6" t="inlineStr"/>
+      <c r="E98" s="28" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n"/>
@@ -2422,7 +2434,7 @@
           <t>Rosewood Lumber</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr"/>
+      <c r="E99" s="28" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n"/>
@@ -2441,7 +2453,7 @@
           <t>Enchanted Wood</t>
         </is>
       </c>
-      <c r="E100" s="6" t="inlineStr"/>
+      <c r="E100" s="28" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n"/>
@@ -2460,7 +2472,7 @@
           <t>Black Forest Elder Tree</t>
         </is>
       </c>
-      <c r="E101" s="6" t="inlineStr"/>
+      <c r="E101" s="28" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n"/>
@@ -2479,7 +2491,7 @@
           <t>Core of the Darkwood</t>
         </is>
       </c>
-      <c r="E102" s="6" t="inlineStr"/>
+      <c r="E102" s="28" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n"/>
@@ -2498,7 +2510,7 @@
           <t>World Tree Bark</t>
         </is>
       </c>
-      <c r="E103" s="6" t="inlineStr"/>
+      <c r="E103" s="28" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n"/>
@@ -2517,7 +2529,7 @@
           <t>Glowing Sap</t>
         </is>
       </c>
-      <c r="E104" s="6" t="inlineStr"/>
+      <c r="E104" s="28" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n"/>
@@ -2536,7 +2548,7 @@
           <t>Sacred Wood</t>
         </is>
       </c>
-      <c r="E105" s="6" t="inlineStr"/>
+      <c r="E105" s="28" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n"/>
@@ -2555,7 +2567,7 @@
           <t>Eternal Growth Ring</t>
         </is>
       </c>
-      <c r="E106" s="6" t="inlineStr"/>
+      <c r="E106" s="28" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n"/>
@@ -2574,7 +2586,7 @@
           <t>World Tree Heartwood</t>
         </is>
       </c>
-      <c r="E107" s="6" t="inlineStr"/>
+      <c r="E107" s="28" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n"/>
@@ -2593,7 +2605,7 @@
           <t>Shard of the Creation Tree</t>
         </is>
       </c>
-      <c r="E108" s="6" t="inlineStr"/>
+      <c r="E108" s="28" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n"/>
@@ -2612,7 +2624,7 @@
           <t>Limestone</t>
         </is>
       </c>
-      <c r="E109" s="6" t="inlineStr"/>
+      <c r="E109" s="28" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n"/>
@@ -2631,7 +2643,7 @@
           <t>Tin Ore</t>
         </is>
       </c>
-      <c r="E110" s="6" t="inlineStr"/>
+      <c r="E110" s="28" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n"/>
@@ -2650,7 +2662,7 @@
           <t>Iron Ore</t>
         </is>
       </c>
-      <c r="E111" s="6" t="inlineStr"/>
+      <c r="E111" s="28" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n"/>
@@ -2669,7 +2681,7 @@
           <t>Platinum Ore</t>
         </is>
       </c>
-      <c r="E112" s="6" t="inlineStr"/>
+      <c r="E112" s="28" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n"/>
@@ -2688,7 +2700,7 @@
           <t>Rough Sapphire</t>
         </is>
       </c>
-      <c r="E113" s="6" t="inlineStr"/>
+      <c r="E113" s="28" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n"/>
@@ -2707,7 +2719,7 @@
           <t>Ley Line Crystal</t>
         </is>
       </c>
-      <c r="E114" s="6" t="inlineStr"/>
+      <c r="E114" s="28" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n"/>
@@ -2726,7 +2738,7 @@
           <t>Basalt</t>
         </is>
       </c>
-      <c r="E115" s="6" t="inlineStr"/>
+      <c r="E115" s="28" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n"/>
@@ -2745,7 +2757,7 @@
           <t>Zinc Ore</t>
         </is>
       </c>
-      <c r="E116" s="6" t="inlineStr"/>
+      <c r="E116" s="28" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n"/>
@@ -2764,7 +2776,7 @@
           <t>Mithril Ore</t>
         </is>
       </c>
-      <c r="E117" s="6" t="inlineStr"/>
+      <c r="E117" s="28" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n"/>
@@ -2783,7 +2795,7 @@
           <t>Rough Ruby</t>
         </is>
       </c>
-      <c r="E118" s="6" t="inlineStr"/>
+      <c r="E118" s="28" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n"/>
@@ -2802,7 +2814,7 @@
           <t>Obsidian Crystal</t>
         </is>
       </c>
-      <c r="E119" s="6" t="inlineStr"/>
+      <c r="E119" s="28" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n"/>
@@ -2821,7 +2833,7 @@
           <t>Earth Core</t>
         </is>
       </c>
-      <c r="E120" s="6" t="inlineStr"/>
+      <c r="E120" s="28" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n"/>
@@ -2840,7 +2852,7 @@
           <t>Crystal Shard</t>
         </is>
       </c>
-      <c r="E121" s="6" t="inlineStr"/>
+      <c r="E121" s="28" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n"/>
@@ -2859,7 +2871,7 @@
           <t>Cobalt Ore</t>
         </is>
       </c>
-      <c r="E122" s="6" t="inlineStr"/>
+      <c r="E122" s="28" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n"/>
@@ -2878,7 +2890,7 @@
           <t>Orichalcum Ore</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr"/>
+      <c r="E123" s="28" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n"/>
@@ -2897,7 +2909,7 @@
           <t>Rough Amethyst</t>
         </is>
       </c>
-      <c r="E124" s="6" t="inlineStr"/>
+      <c r="E124" s="28" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n"/>
@@ -2916,7 +2928,7 @@
           <t>Starlight Ore</t>
         </is>
       </c>
-      <c r="E125" s="6" t="inlineStr"/>
+      <c r="E125" s="28" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n"/>
@@ -2935,7 +2947,7 @@
           <t>Heart of the Cavern</t>
         </is>
       </c>
-      <c r="E126" s="6" t="inlineStr"/>
+      <c r="E126" s="28" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n"/>
@@ -2954,7 +2966,7 @@
           <t>Abyssal Shard</t>
         </is>
       </c>
-      <c r="E127" s="6" t="inlineStr"/>
+      <c r="E127" s="28" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n"/>
@@ -2973,7 +2985,7 @@
           <t>Dark Ore</t>
         </is>
       </c>
-      <c r="E128" s="6" t="inlineStr"/>
+      <c r="E128" s="28" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n"/>
@@ -2992,7 +3004,7 @@
           <t>Adamant Ore</t>
         </is>
       </c>
-      <c r="E129" s="6" t="inlineStr"/>
+      <c r="E129" s="28" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n"/>
@@ -3011,7 +3023,7 @@
           <t>Abyssal Crystal</t>
         </is>
       </c>
-      <c r="E130" s="6" t="inlineStr"/>
+      <c r="E130" s="28" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n"/>
@@ -3030,7 +3042,7 @@
           <t>Molten Star Fragment</t>
         </is>
       </c>
-      <c r="E131" s="6" t="inlineStr"/>
+      <c r="E131" s="28" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n"/>
@@ -3049,7 +3061,7 @@
           <t>Axis of the World</t>
         </is>
       </c>
-      <c r="E132" s="6" t="inlineStr"/>
+      <c r="E132" s="28" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n"/>
@@ -3068,7 +3080,7 @@
           <t>Fox Hide</t>
         </is>
       </c>
-      <c r="E133" s="6" t="inlineStr"/>
+      <c r="E133" s="28" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n"/>
@@ -3087,7 +3099,7 @@
           <t>Boar Tusk</t>
         </is>
       </c>
-      <c r="E134" s="6" t="inlineStr"/>
+      <c r="E134" s="28" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n"/>
@@ -3106,7 +3118,7 @@
           <t>Deer Antler</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr"/>
+      <c r="E135" s="28" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n"/>
@@ -3125,7 +3137,7 @@
           <t>Mountain Lord's Claw</t>
         </is>
       </c>
-      <c r="E136" s="6" t="inlineStr"/>
+      <c r="E136" s="28" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n"/>
@@ -3144,7 +3156,7 @@
           <t>White Tiger Fur</t>
         </is>
       </c>
-      <c r="E137" s="6" t="inlineStr"/>
+      <c r="E137" s="28" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n"/>
@@ -3163,7 +3175,7 @@
           <t>Mountain God's Seal</t>
         </is>
       </c>
-      <c r="E138" s="6" t="inlineStr"/>
+      <c r="E138" s="28" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n"/>
@@ -3182,7 +3194,7 @@
           <t>Leopard Hide</t>
         </is>
       </c>
-      <c r="E139" s="6" t="inlineStr"/>
+      <c r="E139" s="28" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n"/>
@@ -3201,7 +3213,7 @@
           <t>Great Elk Antler</t>
         </is>
       </c>
-      <c r="E140" s="6" t="inlineStr"/>
+      <c r="E140" s="28" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n"/>
@@ -3220,7 +3232,7 @@
           <t>Bear Tooth</t>
         </is>
       </c>
-      <c r="E141" s="6" t="inlineStr"/>
+      <c r="E141" s="28" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n"/>
@@ -3239,7 +3251,7 @@
           <t>Forest Beast's Claw</t>
         </is>
       </c>
-      <c r="E142" s="6" t="inlineStr"/>
+      <c r="E142" s="28" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n"/>
@@ -3258,7 +3270,7 @@
           <t>Ancient Beast Bone</t>
         </is>
       </c>
-      <c r="E143" s="6" t="inlineStr"/>
+      <c r="E143" s="28" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n"/>
@@ -3277,7 +3289,7 @@
           <t>Eye of the Forest Ruler</t>
         </is>
       </c>
-      <c r="E144" s="6" t="inlineStr"/>
+      <c r="E144" s="28" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n"/>
@@ -3296,7 +3308,7 @@
           <t>Snow Leopard Hide</t>
         </is>
       </c>
-      <c r="E145" s="6" t="inlineStr"/>
+      <c r="E145" s="28" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n"/>
@@ -3315,7 +3327,7 @@
           <t>Ice Wolf Fang</t>
         </is>
       </c>
-      <c r="E146" s="6" t="inlineStr"/>
+      <c r="E146" s="28" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n"/>
@@ -3334,7 +3346,7 @@
           <t>Frost Bear Fur</t>
         </is>
       </c>
-      <c r="E147" s="6" t="inlineStr"/>
+      <c r="E147" s="28" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n"/>
@@ -3353,7 +3365,7 @@
           <t>Ice Dragon Scale</t>
         </is>
       </c>
-      <c r="E148" s="6" t="inlineStr"/>
+      <c r="E148" s="28" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n"/>
@@ -3372,7 +3384,7 @@
           <t>Horn of the Snow Peak Lord</t>
         </is>
       </c>
-      <c r="E149" s="6" t="inlineStr"/>
+      <c r="E149" s="28" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n"/>
@@ -3391,7 +3403,7 @@
           <t>Heart of the Permafrost</t>
         </is>
       </c>
-      <c r="E150" s="6" t="inlineStr"/>
+      <c r="E150" s="28" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n"/>
@@ -3410,7 +3422,7 @@
           <t>Monster Hide</t>
         </is>
       </c>
-      <c r="E151" s="6" t="inlineStr"/>
+      <c r="E151" s="28" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n"/>
@@ -3429,7 +3441,7 @@
           <t>Fiend Horn</t>
         </is>
       </c>
-      <c r="E152" s="6" t="inlineStr"/>
+      <c r="E152" s="28" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n"/>
@@ -3448,7 +3460,7 @@
           <t>Fell Beast Fang</t>
         </is>
       </c>
-      <c r="E153" s="6" t="inlineStr"/>
+      <c r="E153" s="28" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n"/>
@@ -3467,7 +3479,7 @@
           <t>Beast King's Mane</t>
         </is>
       </c>
-      <c r="E154" s="6" t="inlineStr"/>
+      <c r="E154" s="28" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n"/>
@@ -3486,7 +3498,7 @@
           <t>Eye of the Abyss Beast</t>
         </is>
       </c>
-      <c r="E155" s="6" t="inlineStr"/>
+      <c r="E155" s="28" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n"/>
@@ -3505,7 +3517,7 @@
           <t>Demon God Fragment</t>
         </is>
       </c>
-      <c r="E156" s="6" t="inlineStr"/>
+      <c r="E156" s="28" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n"/>
@@ -3524,7 +3536,7 @@
           <t>Glass Bead</t>
         </is>
       </c>
-      <c r="E157" s="6" t="inlineStr"/>
+      <c r="E157" s="28" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n"/>
@@ -3543,7 +3555,7 @@
           <t>Amber Bead</t>
         </is>
       </c>
-      <c r="E158" s="6" t="inlineStr"/>
+      <c r="E158" s="28" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n"/>
@@ -3562,7 +3574,7 @@
           <t>Pearl Bead</t>
         </is>
       </c>
-      <c r="E159" s="6" t="inlineStr"/>
+      <c r="E159" s="28" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n"/>
@@ -3581,7 +3593,7 @@
           <t>Opal Bead</t>
         </is>
       </c>
-      <c r="E160" s="6" t="inlineStr"/>
+      <c r="E160" s="28" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n"/>
@@ -3600,7 +3612,7 @@
           <t>Dragon Eye Bead</t>
         </is>
       </c>
-      <c r="E161" s="6" t="inlineStr"/>
+      <c r="E161" s="28" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n"/>
@@ -3619,7 +3631,7 @@
           <t>Bead of Creation</t>
         </is>
       </c>
-      <c r="E162" s="6" t="inlineStr"/>
+      <c r="E162" s="28" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n"/>
@@ -3638,7 +3650,7 @@
           <t>Old Treasure Map</t>
         </is>
       </c>
-      <c r="E163" s="6" t="inlineStr"/>
+      <c r="E163" s="28" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n"/>
@@ -3657,7 +3669,7 @@
           <t>Silver Compass</t>
         </is>
       </c>
-      <c r="E164" s="6" t="inlineStr"/>
+      <c r="E164" s="28" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n"/>
@@ -3676,7 +3688,7 @@
           <t>Golden Key</t>
         </is>
       </c>
-      <c r="E165" s="6" t="inlineStr"/>
+      <c r="E165" s="28" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n"/>
@@ -3695,7 +3707,7 @@
           <t>Enchant Cube</t>
         </is>
       </c>
-      <c r="E166" s="6" t="inlineStr"/>
+      <c r="E166" s="28" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n"/>
@@ -3714,7 +3726,7 @@
           <t>Greater Enchant Cube</t>
         </is>
       </c>
-      <c r="E167" s="6" t="inlineStr"/>
+      <c r="E167" s="28" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n"/>
@@ -3733,7 +3745,7 @@
           <t>Wooden Chest Lv1</t>
         </is>
       </c>
-      <c r="E168" s="6" t="inlineStr"/>
+      <c r="E168" s="28" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n"/>
@@ -3752,7 +3764,7 @@
           <t>Silver Chest Lv1</t>
         </is>
       </c>
-      <c r="E169" s="6" t="inlineStr"/>
+      <c r="E169" s="28" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n"/>
@@ -3771,7 +3783,7 @@
           <t>Golden Chest Lv1</t>
         </is>
       </c>
-      <c r="E170" s="6" t="inlineStr"/>
+      <c r="E170" s="28" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n"/>
@@ -3790,7 +3802,7 @@
           <t>Wooden Chest Lv2</t>
         </is>
       </c>
-      <c r="E171" s="6" t="inlineStr"/>
+      <c r="E171" s="28" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n"/>
@@ -3809,7 +3821,7 @@
           <t>Silver Chest Lv2</t>
         </is>
       </c>
-      <c r="E172" s="6" t="inlineStr"/>
+      <c r="E172" s="28" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n"/>
@@ -3828,7 +3840,7 @@
           <t>Golden Chest Lv2</t>
         </is>
       </c>
-      <c r="E173" s="6" t="inlineStr"/>
+      <c r="E173" s="28" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n"/>
@@ -3847,7 +3859,7 @@
           <t>Wooden Chest Lv3</t>
         </is>
       </c>
-      <c r="E174" s="6" t="inlineStr"/>
+      <c r="E174" s="28" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n"/>
@@ -3866,7 +3878,7 @@
           <t>Silver Chest Lv3</t>
         </is>
       </c>
-      <c r="E175" s="6" t="inlineStr"/>
+      <c r="E175" s="28" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n"/>
@@ -3885,7 +3897,7 @@
           <t>Golden Chest Lv3</t>
         </is>
       </c>
-      <c r="E176" s="6" t="inlineStr"/>
+      <c r="E176" s="28" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n"/>
@@ -3904,7 +3916,7 @@
           <t>Wooden Chest Lv4</t>
         </is>
       </c>
-      <c r="E177" s="6" t="inlineStr"/>
+      <c r="E177" s="28" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n"/>
@@ -3923,7 +3935,7 @@
           <t>Silver Chest Lv4</t>
         </is>
       </c>
-      <c r="E178" s="6" t="inlineStr"/>
+      <c r="E178" s="28" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n"/>
@@ -3942,7 +3954,7 @@
           <t>Golden Chest Lv4</t>
         </is>
       </c>
-      <c r="E179" s="6" t="inlineStr"/>
+      <c r="E179" s="28" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n"/>
@@ -3961,7 +3973,7 @@
           <t>Wooden Chest Lv5</t>
         </is>
       </c>
-      <c r="E180" s="6" t="inlineStr"/>
+      <c r="E180" s="28" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n"/>
@@ -3980,7 +3992,7 @@
           <t>Silver Chest Lv5</t>
         </is>
       </c>
-      <c r="E181" s="6" t="inlineStr"/>
+      <c r="E181" s="28" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n"/>
@@ -3999,7 +4011,7 @@
           <t>Golden Chest Lv5</t>
         </is>
       </c>
-      <c r="E182" s="6" t="inlineStr"/>
+      <c r="E182" s="28" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n"/>
@@ -4018,7 +4030,7 @@
           <t>Growth Potion (S)</t>
         </is>
       </c>
-      <c r="E183" s="6" t="inlineStr"/>
+      <c r="E183" s="28" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n"/>
@@ -4037,7 +4049,7 @@
           <t>Growth Potion (M)</t>
         </is>
       </c>
-      <c r="E184" s="6" t="inlineStr"/>
+      <c r="E184" s="28" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n"/>
@@ -4056,7 +4068,7 @@
           <t>Growth Potion (L)</t>
         </is>
       </c>
-      <c r="E185" s="6" t="inlineStr"/>
+      <c r="E185" s="28" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n"/>
@@ -4075,7 +4087,7 @@
           <t>Elixir of Haste</t>
         </is>
       </c>
-      <c r="E186" s="6" t="inlineStr"/>
+      <c r="E186" s="28" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n"/>
@@ -4094,7 +4106,7 @@
           <t>Elixir of Plenty</t>
         </is>
       </c>
-      <c r="E187" s="6" t="inlineStr"/>
+      <c r="E187" s="28" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n"/>
@@ -4113,7 +4125,7 @@
           <t>Potion of Oblivion</t>
         </is>
       </c>
-      <c r="E188" s="6" t="inlineStr"/>
+      <c r="E188" s="28" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n"/>
@@ -4132,184 +4144,184 @@
           <t>Mana Stone</t>
         </is>
       </c>
-      <c r="E189" s="6" t="inlineStr"/>
+      <c r="E189" s="28" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n"/>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>Item.100061.Name</t>
+          <t>Item.100071.Name</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>흙 묻은 유물</t>
+          <t>캐릭터 뽑기권 A</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>Muddy Relic</t>
-        </is>
-      </c>
-      <c r="E190" s="6" t="inlineStr"/>
+          <t>Character Ticket A</t>
+        </is>
+      </c>
+      <c r="E190" s="28" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n"/>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>Item.100061.Tooltip</t>
+          <t>Item.100071.Tooltip</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>골드 {OpenCostGold}을 내고 감정하면 무언가 나온다</t>
+          <t>열면 희귀 이하 캐릭터 1명이 나온다</t>
         </is>
       </c>
       <c r="D191" s="6" t="inlineStr">
         <is>
-          <t>Pay {OpenCostGold} gold to appraise it and see what's inside</t>
-        </is>
-      </c>
-      <c r="E191" s="6" t="inlineStr"/>
+          <t>Open to get one character of Rare grade or lower</t>
+        </is>
+      </c>
+      <c r="E191" s="28" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n"/>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>Item.100062.Name</t>
+          <t>Item.100072.Name</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>조개 박힌 유물</t>
+          <t>캐릭터 뽑기권 B</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>Shell-Studded Relic</t>
-        </is>
-      </c>
-      <c r="E192" s="6" t="inlineStr"/>
+          <t>Character Ticket B</t>
+        </is>
+      </c>
+      <c r="E192" s="28" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n"/>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>Item.100062.Tooltip</t>
+          <t>Item.100072.Tooltip</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>골드 {OpenCostGold}을 내고 감정하면 무언가 나온다</t>
+          <t>열면 영웅 이하 캐릭터 1명이 나온다</t>
         </is>
       </c>
       <c r="D193" s="6" t="inlineStr">
         <is>
-          <t>Pay {OpenCostGold} gold to appraise it and see what's inside</t>
-        </is>
-      </c>
-      <c r="E193" s="6" t="inlineStr"/>
+          <t>Open to get one character of Epic grade or lower</t>
+        </is>
+      </c>
+      <c r="E193" s="28" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n"/>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>Item.100063.Name</t>
+          <t>Item.100073.Name</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>산호 엉긴 유물</t>
+          <t>캐릭터 뽑기권 C</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>Coral-Crusted Relic</t>
-        </is>
-      </c>
-      <c r="E194" s="6" t="inlineStr"/>
+          <t>Character Ticket C</t>
+        </is>
+      </c>
+      <c r="E194" s="28" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n"/>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>Item.100063.Tooltip</t>
+          <t>Item.100073.Tooltip</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>골드 {OpenCostGold}을 내고 감정하면 무언가 나온다</t>
+          <t>열면 전설 이하 캐릭터 1명이 나온다</t>
         </is>
       </c>
       <c r="D195" s="6" t="inlineStr">
         <is>
-          <t>Pay {OpenCostGold} gold to appraise it and see what's inside</t>
-        </is>
-      </c>
-      <c r="E195" s="6" t="inlineStr"/>
+          <t>Open to get one character of Legendary grade or lower</t>
+        </is>
+      </c>
+      <c r="E195" s="28" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n"/>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>Item.100064.Name</t>
+          <t>Item.100074.Name</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
         <is>
-          <t>봉인된 유물</t>
+          <t>캐릭터 뽑기권 D</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>Sealed Relic</t>
-        </is>
-      </c>
-      <c r="E196" s="6" t="inlineStr"/>
+          <t>Character Ticket D</t>
+        </is>
+      </c>
+      <c r="E196" s="28" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n"/>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>Item.100064.Tooltip</t>
+          <t>Item.100074.Tooltip</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>골드 {OpenCostGold}을 내고 감정하면 무언가 나온다</t>
+          <t>열면 신화 이하 캐릭터 1명이 나온다</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>Pay {OpenCostGold} gold to appraise it and see what's inside</t>
-        </is>
-      </c>
-      <c r="E197" s="6" t="inlineStr"/>
+          <t>Open to get one character of Mythic grade or lower</t>
+        </is>
+      </c>
+      <c r="E197" s="28" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n"/>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>Item.100065.Name</t>
+          <t>Item.100061.Name</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t>황금 띠 유물</t>
+          <t>흙 묻은 유물</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>Gold-Banded Relic</t>
-        </is>
-      </c>
-      <c r="E198" s="6" t="inlineStr"/>
+          <t>Muddy Relic</t>
+        </is>
+      </c>
+      <c r="E198" s="28" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n"/>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>Item.100065.Tooltip</t>
+          <t>Item.100061.Tooltip</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
@@ -4322,32 +4334,32 @@
           <t>Pay {OpenCostGold} gold to appraise it and see what's inside</t>
         </is>
       </c>
-      <c r="E199" s="6" t="inlineStr"/>
+      <c r="E199" s="28" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n"/>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>Item.100066.Name</t>
+          <t>Item.100062.Name</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>왕의 유물</t>
+          <t>조개 박힌 유물</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>King's Relic</t>
-        </is>
-      </c>
-      <c r="E200" s="6" t="inlineStr"/>
+          <t>Shell-Studded Relic</t>
+        </is>
+      </c>
+      <c r="E200" s="28" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n"/>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>Item.100066.Tooltip</t>
+          <t>Item.100062.Tooltip</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
@@ -4360,45 +4372,197 @@
           <t>Pay {OpenCostGold} gold to appraise it and see what's inside</t>
         </is>
       </c>
-      <c r="E201" s="6" t="inlineStr"/>
+      <c r="E201" s="28" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n"/>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>Item.100067.Name</t>
+          <t>Item.100063.Name</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
         <is>
-          <t>무지개 유물</t>
+          <t>산호 엉긴 유물</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>Rainbow Relic</t>
-        </is>
-      </c>
-      <c r="E202" s="6" t="inlineStr"/>
+          <t>Coral-Crusted Relic</t>
+        </is>
+      </c>
+      <c r="E202" s="28" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n"/>
       <c r="B203" s="6" t="inlineStr">
         <is>
+          <t>Item.100063.Tooltip</t>
+        </is>
+      </c>
+      <c r="C203" s="6" t="inlineStr">
+        <is>
+          <t>골드 {OpenCostGold}을 내고 감정하면 무언가 나온다</t>
+        </is>
+      </c>
+      <c r="D203" s="6" t="inlineStr">
+        <is>
+          <t>Pay {OpenCostGold} gold to appraise it and see what's inside</t>
+        </is>
+      </c>
+      <c r="E203" s="28" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n"/>
+      <c r="B204" s="6" t="inlineStr">
+        <is>
+          <t>Item.100064.Name</t>
+        </is>
+      </c>
+      <c r="C204" s="6" t="inlineStr">
+        <is>
+          <t>봉인된 유물</t>
+        </is>
+      </c>
+      <c r="D204" s="6" t="inlineStr">
+        <is>
+          <t>Sealed Relic</t>
+        </is>
+      </c>
+      <c r="E204" s="28" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n"/>
+      <c r="B205" s="6" t="inlineStr">
+        <is>
+          <t>Item.100064.Tooltip</t>
+        </is>
+      </c>
+      <c r="C205" s="6" t="inlineStr">
+        <is>
+          <t>골드 {OpenCostGold}을 내고 감정하면 무언가 나온다</t>
+        </is>
+      </c>
+      <c r="D205" s="6" t="inlineStr">
+        <is>
+          <t>Pay {OpenCostGold} gold to appraise it and see what's inside</t>
+        </is>
+      </c>
+      <c r="E205" s="28" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n"/>
+      <c r="B206" s="6" t="inlineStr">
+        <is>
+          <t>Item.100065.Name</t>
+        </is>
+      </c>
+      <c r="C206" s="6" t="inlineStr">
+        <is>
+          <t>황금 띠 유물</t>
+        </is>
+      </c>
+      <c r="D206" s="6" t="inlineStr">
+        <is>
+          <t>Gold-Banded Relic</t>
+        </is>
+      </c>
+      <c r="E206" s="28" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n"/>
+      <c r="B207" s="6" t="inlineStr">
+        <is>
+          <t>Item.100065.Tooltip</t>
+        </is>
+      </c>
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>골드 {OpenCostGold}을 내고 감정하면 무언가 나온다</t>
+        </is>
+      </c>
+      <c r="D207" s="6" t="inlineStr">
+        <is>
+          <t>Pay {OpenCostGold} gold to appraise it and see what's inside</t>
+        </is>
+      </c>
+      <c r="E207" s="28" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n"/>
+      <c r="B208" s="6" t="inlineStr">
+        <is>
+          <t>Item.100066.Name</t>
+        </is>
+      </c>
+      <c r="C208" s="6" t="inlineStr">
+        <is>
+          <t>왕의 유물</t>
+        </is>
+      </c>
+      <c r="D208" s="6" t="inlineStr">
+        <is>
+          <t>King's Relic</t>
+        </is>
+      </c>
+      <c r="E208" s="28" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n"/>
+      <c r="B209" s="6" t="inlineStr">
+        <is>
+          <t>Item.100066.Tooltip</t>
+        </is>
+      </c>
+      <c r="C209" s="6" t="inlineStr">
+        <is>
+          <t>골드 {OpenCostGold}을 내고 감정하면 무언가 나온다</t>
+        </is>
+      </c>
+      <c r="D209" s="6" t="inlineStr">
+        <is>
+          <t>Pay {OpenCostGold} gold to appraise it and see what's inside</t>
+        </is>
+      </c>
+      <c r="E209" s="28" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n"/>
+      <c r="B210" s="6" t="inlineStr">
+        <is>
+          <t>Item.100067.Name</t>
+        </is>
+      </c>
+      <c r="C210" s="6" t="inlineStr">
+        <is>
+          <t>무지개 유물</t>
+        </is>
+      </c>
+      <c r="D210" s="6" t="inlineStr">
+        <is>
+          <t>Rainbow Relic</t>
+        </is>
+      </c>
+      <c r="E210" s="28" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n"/>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
           <t>Item.100067.Tooltip</t>
         </is>
       </c>
-      <c r="C203" s="6" t="inlineStr">
+      <c r="C211" s="6" t="inlineStr">
         <is>
           <t>골드 {OpenCostGold}을 내고 감정하면 무언가 나온다</t>
         </is>
       </c>
-      <c r="D203" s="6" t="inlineStr">
+      <c r="D211" s="6" t="inlineStr">
         <is>
           <t>Pay {OpenCostGold} gold to appraise it and see what's inside</t>
         </is>
       </c>
-      <c r="E203" s="6" t="inlineStr"/>
+      <c r="E211" s="28" t="inlineStr"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
